--- a/data/trans_dic/P56$familiarvive-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiarvive-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,83; 33,91</t>
+          <t>10,91; 34,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,8; 32,59</t>
+          <t>9,34; 31,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,57; 30,26</t>
+          <t>11,64; 31,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 17,13</t>
+          <t>5,59; 16,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,98; 55,76</t>
+          <t>33,09; 55,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,69; 34,91</t>
+          <t>21,25; 34,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,68; 35,32</t>
+          <t>19,21; 35,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,74; 27,43</t>
+          <t>18,63; 26,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,54; 43,91</t>
+          <t>27,69; 44,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,21; 31,45</t>
+          <t>20,39; 32,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,22; 31,45</t>
+          <t>18,78; 31,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,17; 23,4</t>
+          <t>15,95; 23,02</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,2; 67,78</t>
+          <t>11,14; 68,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,74</t>
+          <t>0,0; 29,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,74; 35,47</t>
+          <t>8,86; 34,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,41</t>
+          <t>0,0; 83,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,89; 75,22</t>
+          <t>11,31; 74,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,88; 57,59</t>
+          <t>14,89; 59,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,87; 25,11</t>
+          <t>9,9; 26,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,03</t>
+          <t>0,0; 58,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,63; 61,09</t>
+          <t>15,93; 61,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,35; 43,46</t>
+          <t>10,17; 42,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,46; 24,95</t>
+          <t>11,48; 24,79</t>
         </is>
       </c>
     </row>
@@ -1002,22 +1002,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,4</t>
+          <t>0,0; 51,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,17 +1027,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,78; 53,73</t>
+          <t>5,73; 55,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,6; 41,44</t>
+          <t>6,86; 44,84</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 31,83</t>
+          <t>9,98; 31,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,0; 32,85</t>
+          <t>11,3; 32,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,08; 27,03</t>
+          <t>9,8; 25,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,41; 19,63</t>
+          <t>8,57; 20,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,8; 51,58</t>
+          <t>30,49; 51,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,72; 35,45</t>
+          <t>22,47; 35,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,26; 34,14</t>
+          <t>19,54; 34,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,86; 25,61</t>
+          <t>18,24; 25,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,87; 41,88</t>
+          <t>26,57; 41,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,76; 32,84</t>
+          <t>20,91; 32,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,0; 29,82</t>
+          <t>18,4; 29,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,05; 22,13</t>
+          <t>16,07; 22,14</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4782; 14964</t>
+          <t>4815; 15260</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6704; 22292</t>
+          <t>6385; 21345</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6561; 17155</t>
+          <t>6601; 18000</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3847; 11632</t>
+          <t>3797; 11419</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27508; 46515</t>
+          <t>27599; 46664</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40326; 64921</t>
+          <t>39519; 64869</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26666; 50410</t>
+          <t>27416; 50738</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37586; 55007</t>
+          <t>37356; 54012</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33851; 56004</t>
+          <t>35318; 57158</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51405; 79982</t>
+          <t>51861; 81652</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36336; 62715</t>
+          <t>37443; 63434</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>43410; 62832</t>
+          <t>42832; 61788</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1268</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1022; 6185</t>
+          <t>1017; 6207</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3437</t>
+          <t>0; 3301</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2639; 9613</t>
+          <t>2402; 9255</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4834</t>
+          <t>0; 5648</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1163; 8848</t>
+          <t>1330; 8720</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3270; 14618</t>
+          <t>3781; 15094</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3732; 10564</t>
+          <t>4167; 11144</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5679</t>
+          <t>0; 6346</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3475; 12760</t>
+          <t>3327; 12800</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3784; 15889</t>
+          <t>3720; 15663</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7930; 17263</t>
+          <t>7938; 17147</t>
         </is>
       </c>
     </row>
@@ -1925,22 +1925,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 761</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1877</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3523</t>
+          <t>0; 3361</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1493</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1950,17 +1950,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1630</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>374; 3476</t>
+          <t>371; 3622</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1493</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2086</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>596; 5365</t>
+          <t>888; 5805</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4792; 15366</t>
+          <t>4817; 15129</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9419; 25791</t>
+          <t>8874; 25277</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7267; 19490</t>
+          <t>7062; 18504</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8536; 19919</t>
+          <t>8700; 20582</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28816; 48252</t>
+          <t>28525; 48161</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45919; 71654</t>
+          <t>45416; 70799</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33081; 58651</t>
+          <t>33564; 59659</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44491; 63798</t>
+          <t>45448; 63414</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36686; 59390</t>
+          <t>37688; 59486</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58259; 92168</t>
+          <t>58692; 90201</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43897; 72721</t>
+          <t>44872; 73135</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>56266; 77594</t>
+          <t>56351; 77628</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$familiarvive-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiarvive-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,91; 34,58</t>
+          <t>10,93; 34,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,34; 31,21</t>
+          <t>9,96; 31,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,64; 31,75</t>
+          <t>11,9; 31,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,59; 16,82</t>
+          <t>5,2; 16,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,09; 55,94</t>
+          <t>31,99; 53,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,25; 34,89</t>
+          <t>21,28; 34,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,21; 35,55</t>
+          <t>18,34; 36,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,63; 26,93</t>
+          <t>18,59; 27,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,69; 44,81</t>
+          <t>27,62; 45,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,39; 32,1</t>
+          <t>20,6; 31,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,78; 31,81</t>
+          <t>18,71; 31,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,95; 23,02</t>
+          <t>16,32; 23,37</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,14; 68,01</t>
+          <t>10,84; 68,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,53</t>
+          <t>0,0; 37,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,86; 34,15</t>
+          <t>9,23; 34,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,44</t>
+          <t>0,0; 80,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,31; 74,13</t>
+          <t>9,82; 74,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,89; 59,46</t>
+          <t>13,05; 54,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,9; 26,49</t>
+          <t>9,29; 24,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,15</t>
+          <t>0,0; 51,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,93; 61,27</t>
+          <t>16,67; 61,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,17; 42,84</t>
+          <t>10,73; 42,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,48; 24,79</t>
+          <t>11,39; 25,23</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,9</t>
+          <t>0,0; 47,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 55,98</t>
+          <t>4,92; 47,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,86; 44,84</t>
+          <t>5,6; 38,46</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,98; 31,33</t>
+          <t>9,48; 31,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,3; 32,2</t>
+          <t>10,89; 31,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,8; 25,67</t>
+          <t>9,32; 25,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 20,28</t>
+          <t>8,49; 19,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,49; 51,48</t>
+          <t>30,27; 51,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,47; 35,03</t>
+          <t>22,38; 35,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,54; 34,73</t>
+          <t>19,62; 34,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,24; 25,46</t>
+          <t>17,8; 25,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,57; 41,94</t>
+          <t>26,23; 41,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,91; 32,14</t>
+          <t>20,97; 32,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,4; 29,99</t>
+          <t>18,57; 29,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,07; 22,14</t>
+          <t>16,17; 22,21</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>45482</t>
+          <t>49385</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52386</t>
+          <t>56909</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4815; 15260</t>
+          <t>4824; 15270</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6385; 21345</t>
+          <t>6813; 21820</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6601; 18000</t>
+          <t>6743; 17887</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3797; 11419</t>
+          <t>3757; 12107</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27599; 46664</t>
+          <t>26687; 44490</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39519; 64869</t>
+          <t>39571; 64661</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27416; 50738</t>
+          <t>26177; 51821</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37356; 54012</t>
+          <t>40367; 59223</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35318; 57158</t>
+          <t>35232; 57687</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51861; 81652</t>
+          <t>52400; 81356</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37443; 63434</t>
+          <t>37302; 62655</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42832; 61788</t>
+          <t>47237; 67647</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>7654</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>13465</t>
         </is>
       </c>
     </row>
@@ -1717,57 +1717,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1017; 6207</t>
+          <t>990; 6210</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3301</t>
+          <t>0; 4208</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2402; 9255</t>
+          <t>2638; 9868</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5648</t>
+          <t>0; 5415</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1330; 8720</t>
+          <t>1155; 8749</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3781; 15094</t>
+          <t>3313; 13852</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4167; 11144</t>
+          <t>4467; 11973</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6346</t>
+          <t>0; 5575</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3327; 12800</t>
+          <t>3482; 12897</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3720; 15663</t>
+          <t>3922; 15415</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7938; 17147</t>
+          <t>8730; 19341</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2576</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3361</t>
+          <t>0; 3402</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>371; 3622</t>
+          <t>402; 3916</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>888; 5805</t>
+          <t>858; 5891</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>53643</t>
+          <t>58690</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66911</t>
+          <t>72950</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4817; 15129</t>
+          <t>4577; 15035</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8874; 25277</t>
+          <t>8549; 24337</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7062; 18504</t>
+          <t>6720; 18714</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8700; 20582</t>
+          <t>9165; 21451</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28525; 48161</t>
+          <t>28318; 48416</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45416; 70799</t>
+          <t>45243; 71317</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33564; 59659</t>
+          <t>33698; 59433</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45448; 63414</t>
+          <t>48655; 69294</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37688; 59486</t>
+          <t>37203; 58298</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58692; 90201</t>
+          <t>58838; 90932</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44872; 73135</t>
+          <t>45284; 73120</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>56351; 77628</t>
+          <t>61681; 84690</t>
         </is>
       </c>
     </row>
